--- a/data/trans_orig/P33B4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023</t>
+          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>36708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64850</t>
+          <t>65946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71154</t>
+          <t>71794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95203</t>
+          <t>96751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>112556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153053</t>
+          <t>151550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28463</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56102</t>
+          <t>53605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>59044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86171</t>
+          <t>84947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94036</t>
+          <t>93785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130365</t>
+          <t>130140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95113</t>
+          <t>96343</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135254</t>
+          <t>130760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137507</t>
+          <t>137752</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170441</t>
+          <t>169851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240875</t>
+          <t>245347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>290073</t>
+          <t>294523</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>408291</t>
+          <t>408356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>458921</t>
+          <t>457007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>346535</t>
+          <t>343920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>387894</t>
+          <t>387755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>770015</t>
+          <t>768745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>836088</t>
+          <t>833911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35722</t>
+          <t>32939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92504</t>
+          <t>94506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102673</t>
+          <t>101951</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>134950</t>
+          <t>135568</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>121009</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>219439</t>
+          <t>218905</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29994</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77798</t>
+          <t>80837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81665</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110306</t>
+          <t>109927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98353</t>
+          <t>100899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179070</t>
+          <t>181955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76800</t>
+          <t>67216</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192740</t>
+          <t>194335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>194365</t>
+          <t>193298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>233714</t>
+          <t>233358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>235603</t>
+          <t>250965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>418058</t>
+          <t>418754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>842860</t>
+          <t>839052</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1048803</t>
+          <t>1072756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>502226</t>
+          <t>504542</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>556721</t>
+          <t>555402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1353170</t>
+          <t>1348864</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1680895</t>
+          <t>1677071</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>55624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84795</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66523</t>
+          <t>68802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125355</t>
+          <t>128598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57783</t>
+          <t>58859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41399</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>107748</t>
+          <t>106990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>79071</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>147659</t>
+          <t>147899</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103639</t>
+          <t>103516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150496</t>
+          <t>149389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74742</t>
+          <t>67981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182343</t>
+          <t>181853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>174800</t>
+          <t>172328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311965</t>
+          <t>309718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468472</t>
+          <t>467422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>522821</t>
+          <t>521876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>568073</t>
+          <t>569898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>780004</t>
+          <t>795763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1070384</t>
+          <t>1074611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318297</t>
+          <t>1312421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57649</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93422</t>
+          <t>91584</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107769</t>
+          <t>106456</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153777</t>
+          <t>153833</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178104</t>
+          <t>179038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236077</t>
+          <t>234476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60124</t>
+          <t>61896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94497</t>
+          <t>94074</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137152</t>
+          <t>137701</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161436</t>
+          <t>159646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219425</t>
+          <t>218271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>127724</t>
+          <t>128407</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>172416</t>
+          <t>175377</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>168793</t>
+          <t>171894</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>241627</t>
+          <t>241568</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>323564</t>
+          <t>321058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>400356</t>
+          <t>401438</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>594052</t>
+          <t>595666</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>652969</t>
+          <t>656020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>592352</t>
+          <t>587964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>721114</t>
+          <t>722580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1206204</t>
+          <t>1209735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1339594</t>
+          <t>1340574</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>181082</t>
+          <t>177369</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>269016</t>
+          <t>263324</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>322468</t>
+          <t>325484</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>439173</t>
+          <t>442484</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>542694</t>
+          <t>539818</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>685879</t>
+          <t>688374</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166969</t>
+          <t>165236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>252133</t>
+          <t>245787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>291459</t>
+          <t>294772</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>395914</t>
+          <t>398918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>492553</t>
+          <t>489633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>629771</t>
+          <t>628626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>416153</t>
+          <t>420911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>596419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>558095</t>
+          <t>593034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776492</t>
+          <t>780988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1101163</t>
+          <t>1082395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1350563</t>
+          <t>1353174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2376978</t>
+          <t>2386119</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2696543</t>
+          <t>2698960</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2069052</t>
+          <t>2063538</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2499607</t>
+          <t>2469347</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4493867</t>
+          <t>4487466</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4959207</t>
+          <t>5001639</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48745</t>
+          <t>53785</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36708</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65946</t>
+          <t>71138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>82577</t>
+          <t>91143</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71794</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96751</t>
+          <t>106192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>131323</t>
+          <t>144928</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112556</t>
+          <t>123869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151550</t>
+          <t>166117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38223</t>
+          <t>43518</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53605</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71918</t>
+          <t>78406</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59044</t>
+          <t>66079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84947</t>
+          <t>93463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110140</t>
+          <t>121923</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93785</t>
+          <t>103331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130140</t>
+          <t>143617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113458</t>
+          <t>122270</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96343</t>
+          <t>103864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130760</t>
+          <t>142637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153021</t>
+          <t>162367</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137752</t>
+          <t>146355</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169851</t>
+          <t>180528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>266479</t>
+          <t>284636</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245347</t>
+          <t>257065</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>294523</t>
+          <t>312888</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>433986</t>
+          <t>470055</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>408356</t>
+          <t>445562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>457007</t>
+          <t>496209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>400392</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>343920</t>
+          <t>379781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>387755</t>
+          <t>423009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>801434</t>
+          <t>870447</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>768745</t>
+          <t>835695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>833911</t>
+          <t>905353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674963</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674963</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674963</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1309375</t>
+          <t>1421934</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309375</t>
+          <t>1421934</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1309375</t>
+          <t>1421934</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>76126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32939</t>
+          <t>59444</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94506</t>
+          <t>97054</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118393</t>
+          <t>131501</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101951</t>
+          <t>112482</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135568</t>
+          <t>150055</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>186128</t>
+          <t>207628</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>121009</t>
+          <t>183358</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>218905</t>
+          <t>237841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>8,66%</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>60541</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>46328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80837</t>
+          <t>76813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>95371</t>
+          <t>106253</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80678</t>
+          <t>92485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109927</t>
+          <t>123622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>151374</t>
+          <t>166794</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100899</t>
+          <t>144727</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181955</t>
+          <t>191338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>145997</t>
+          <t>157670</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67216</t>
+          <t>133287</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194335</t>
+          <t>183796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>213578</t>
+          <t>235734</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193298</t>
+          <t>212300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>233358</t>
+          <t>257442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>359574</t>
+          <t>393404</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250965</t>
+          <t>363495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>418754</t>
+          <t>427315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>922160</t>
+          <t>753591</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>839052</t>
+          <t>721470</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1072756</t>
+          <t>782986</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>530118</t>
+          <t>596610</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>504542</t>
+          <t>569924</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>555402</t>
+          <t>628028</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1452278</t>
+          <t>1350201</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1348864</t>
+          <t>1308116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1677071</t>
+          <t>1392648</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2149355</t>
+          <t>2118027</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2149355</t>
+          <t>2118027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2149355</t>
+          <t>2118027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>46142</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>34084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55624</t>
+          <t>61387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61009</t>
+          <t>72443</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27977</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84008</t>
+          <t>91630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>102140</t>
+          <t>118585</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68802</t>
+          <t>97159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128598</t>
+          <t>140448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>35034</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58859</t>
+          <t>64062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77137</t>
+          <t>90548</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>74592</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>106990</t>
+          <t>109581</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119493</t>
+          <t>137705</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79071</t>
+          <t>114532</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>147899</t>
+          <t>159718</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>126431</t>
+          <t>149960</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103516</t>
+          <t>127208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149389</t>
+          <t>177548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>134947</t>
+          <t>160558</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>139562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181853</t>
+          <t>180293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>261378</t>
+          <t>310518</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172328</t>
+          <t>278860</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>309718</t>
+          <t>342811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>494761</t>
+          <t>559814</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467422</t>
+          <t>528900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>521876</t>
+          <t>586109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>660274</t>
+          <t>488710</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>569898</t>
+          <t>463028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>795763</t>
+          <t>513161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1155034</t>
+          <t>1048524</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1074611</t>
+          <t>1007644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1312421</t>
+          <t>1089000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72534</t>
+          <t>79929</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>62617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91584</t>
+          <t>97510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>133697</t>
+          <t>151579</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106456</t>
+          <t>133426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153833</t>
+          <t>172942</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>206231</t>
+          <t>231508</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>179038</t>
+          <t>204958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234476</t>
+          <t>258240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>76080</t>
+          <t>80652</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61896</t>
+          <t>64248</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94074</t>
+          <t>100381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>112853</t>
+          <t>118815</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89876</t>
+          <t>102243</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137701</t>
+          <t>138695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>188932</t>
+          <t>199466</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>159646</t>
+          <t>177385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>218271</t>
+          <t>226603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>149785</t>
+          <t>159248</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>128407</t>
+          <t>138033</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>175377</t>
+          <t>185097</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>214470</t>
+          <t>232427</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>171894</t>
+          <t>211735</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>241568</t>
+          <t>255715</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>364255</t>
+          <t>391675</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>321058</t>
+          <t>357654</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>401438</t>
+          <t>423889</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -2771,22 +2771,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>627417</t>
+          <t>669255</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>595666</t>
+          <t>636365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>656020</t>
+          <t>698014</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>631573</t>
+          <t>615498</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>587964</t>
+          <t>583335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>722580</t>
+          <t>642909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1258990</t>
+          <t>1284753</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1209735</t>
+          <t>1243574</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1340574</t>
+          <t>1328216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989084</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989084</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989084</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2018408</t>
+          <t>2107403</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2018408</t>
+          <t>2107403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2018408</t>
+          <t>2107403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>230145</t>
+          <t>255982</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177369</t>
+          <t>225833</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>263324</t>
+          <t>293588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>395677</t>
+          <t>446667</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>325484</t>
+          <t>413139</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>442484</t>
+          <t>482837</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>625822</t>
+          <t>702649</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>539818</t>
+          <t>658065</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>688374</t>
+          <t>746046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>212662</t>
+          <t>231868</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>165236</t>
+          <t>202198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>265009</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>357278</t>
+          <t>394021</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>294772</t>
+          <t>364310</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>398918</t>
+          <t>429016</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>569940</t>
+          <t>625889</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>489633</t>
+          <t>583161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>628626</t>
+          <t>670415</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>535671</t>
+          <t>589148</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>420911</t>
+          <t>544484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>596419</t>
+          <t>634522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>716015</t>
+          <t>791085</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>593034</t>
+          <t>752845</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>780988</t>
+          <t>834586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1251686</t>
+          <t>1380233</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1082395</t>
+          <t>1322087</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1353174</t>
+          <t>1450693</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2478324</t>
+          <t>2452716</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2386119</t>
+          <t>2389852</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2698960</t>
+          <t>2511758</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2189412</t>
+          <t>2101209</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2063538</t>
+          <t>2049436</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2469347</t>
+          <t>2150649</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4667736</t>
+          <t>4553925</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4487466</t>
+          <t>4468313</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5001639</t>
+          <t>4630232</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
